--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131560</v>
+        <v>122131533</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>92030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572083</v>
+        <v>572000</v>
       </c>
       <c r="R2" t="n">
-        <v>7108040</v>
+        <v>7108033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>122131506</v>
       </c>
       <c r="B3" t="n">
-        <v>78368</v>
+        <v>78375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131533</v>
+        <v>122131620</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>79748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572000</v>
+        <v>572081</v>
       </c>
       <c r="R4" t="n">
-        <v>7108033</v>
+        <v>7108048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131581</v>
+        <v>122131560</v>
       </c>
       <c r="B5" t="n">
-        <v>78369</v>
+        <v>79257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572092</v>
+        <v>572083</v>
       </c>
       <c r="R5" t="n">
-        <v>7108069</v>
+        <v>7108040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>August Alvtegen, Johanna Kühne</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131620</v>
+        <v>122131581</v>
       </c>
       <c r="B6" t="n">
-        <v>79741</v>
+        <v>78376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572081</v>
+        <v>572092</v>
       </c>
       <c r="R6" t="n">
-        <v>7108048</v>
+        <v>7108069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131506</v>
+        <v>122131560</v>
       </c>
       <c r="B3" t="n">
-        <v>78381</v>
+        <v>79263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572090</v>
+        <v>572083</v>
       </c>
       <c r="R3" t="n">
-        <v>7108068</v>
+        <v>7108040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Johanna Kühne, August Alvtegen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131533</v>
+        <v>122131620</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>79754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572000</v>
+        <v>572081</v>
       </c>
       <c r="R4" t="n">
-        <v>7108033</v>
+        <v>7108048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131560</v>
+        <v>122131533</v>
       </c>
       <c r="B5" t="n">
-        <v>79263</v>
+        <v>92055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572083</v>
+        <v>572000</v>
       </c>
       <c r="R5" t="n">
-        <v>7108040</v>
+        <v>7108033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131620</v>
+        <v>122131506</v>
       </c>
       <c r="B6" t="n">
-        <v>79754</v>
+        <v>78381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572081</v>
+        <v>572090</v>
       </c>
       <c r="R6" t="n">
-        <v>7108048</v>
+        <v>7108068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131581</v>
       </c>
       <c r="B2" t="n">
-        <v>78382</v>
+        <v>78383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131560</v>
+        <v>122131533</v>
       </c>
       <c r="B3" t="n">
-        <v>79263</v>
+        <v>92065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572083</v>
+        <v>572000</v>
       </c>
       <c r="R3" t="n">
-        <v>7108040</v>
+        <v>7108033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>122131620</v>
       </c>
       <c r="B4" t="n">
-        <v>79754</v>
+        <v>79755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131533</v>
+        <v>122131560</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>79264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572000</v>
+        <v>572083</v>
       </c>
       <c r="R5" t="n">
-        <v>7108033</v>
+        <v>7108040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Johanna Kühne, August Alvtegen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>122131506</v>
       </c>
       <c r="B6" t="n">
-        <v>78381</v>
+        <v>78382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131581</v>
+        <v>122131560</v>
       </c>
       <c r="B2" t="n">
-        <v>78383</v>
+        <v>79264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572092</v>
+        <v>572083</v>
       </c>
       <c r="R2" t="n">
-        <v>7108069</v>
+        <v>7108040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Johanna Kühne, August Alvtegen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131533</v>
+        <v>122131581</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>78383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572000</v>
+        <v>572092</v>
       </c>
       <c r="R3" t="n">
-        <v>7108033</v>
+        <v>7108069</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131620</v>
+        <v>122131506</v>
       </c>
       <c r="B4" t="n">
-        <v>79755</v>
+        <v>78382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572081</v>
+        <v>572090</v>
       </c>
       <c r="R4" t="n">
-        <v>7108048</v>
+        <v>7108068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131560</v>
+        <v>122131620</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572083</v>
+        <v>572081</v>
       </c>
       <c r="R5" t="n">
-        <v>7108040</v>
+        <v>7108048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131506</v>
+        <v>122131533</v>
       </c>
       <c r="B6" t="n">
-        <v>78382</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572090</v>
+        <v>572000</v>
       </c>
       <c r="R6" t="n">
-        <v>7108068</v>
+        <v>7108033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131560</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131581</v>
+        <v>122131533</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>92077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572092</v>
+        <v>572000</v>
       </c>
       <c r="R3" t="n">
-        <v>7108069</v>
+        <v>7108033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131506</v>
+        <v>122131581</v>
       </c>
       <c r="B4" t="n">
-        <v>78382</v>
+        <v>78388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572090</v>
+        <v>572092</v>
       </c>
       <c r="R4" t="n">
-        <v>7108068</v>
+        <v>7108069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>122131620</v>
       </c>
       <c r="B5" t="n">
-        <v>79755</v>
+        <v>79760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131533</v>
+        <v>122131506</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>78387</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572000</v>
+        <v>572090</v>
       </c>
       <c r="R6" t="n">
-        <v>7108033</v>
+        <v>7108068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131560</v>
+        <v>122131581</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>78388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572083</v>
+        <v>572092</v>
       </c>
       <c r="R2" t="n">
-        <v>7108040</v>
+        <v>7108069</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>122131533</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131581</v>
+        <v>122131506</v>
       </c>
       <c r="B4" t="n">
-        <v>78388</v>
+        <v>78387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572092</v>
+        <v>572090</v>
       </c>
       <c r="R4" t="n">
-        <v>7108069</v>
+        <v>7108068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131620</v>
+        <v>122131560</v>
       </c>
       <c r="B5" t="n">
-        <v>79760</v>
+        <v>79269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572081</v>
+        <v>572083</v>
       </c>
       <c r="R5" t="n">
-        <v>7108048</v>
+        <v>7108040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>August Alvtegen, Johanna Kühne</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131506</v>
+        <v>122131620</v>
       </c>
       <c r="B6" t="n">
-        <v>78387</v>
+        <v>79760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572090</v>
+        <v>572081</v>
       </c>
       <c r="R6" t="n">
-        <v>7108068</v>
+        <v>7108048</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131581</v>
+        <v>122131533</v>
       </c>
       <c r="B2" t="n">
-        <v>78388</v>
+        <v>92087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572092</v>
+        <v>572000</v>
       </c>
       <c r="R2" t="n">
-        <v>7108069</v>
+        <v>7108033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131533</v>
+        <v>122131560</v>
       </c>
       <c r="B3" t="n">
-        <v>92082</v>
+        <v>79270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +784,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572000</v>
+        <v>572083</v>
       </c>
       <c r="R3" t="n">
-        <v>7108033</v>
+        <v>7108040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>August Alvtegen, Johanna Kühne</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131506</v>
+        <v>122131620</v>
       </c>
       <c r="B4" t="n">
-        <v>78387</v>
+        <v>79761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +881,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>6461</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572090</v>
+        <v>572081</v>
       </c>
       <c r="R4" t="n">
-        <v>7108068</v>
+        <v>7108048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131560</v>
+        <v>122131581</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>78389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +982,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572083</v>
+        <v>572092</v>
       </c>
       <c r="R5" t="n">
-        <v>7108040</v>
+        <v>7108069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen, Johanna Kühne</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131620</v>
+        <v>122131506</v>
       </c>
       <c r="B6" t="n">
-        <v>79760</v>
+        <v>78388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1075,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572081</v>
+        <v>572090</v>
       </c>
       <c r="R6" t="n">
-        <v>7108048</v>
+        <v>7108068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131533</v>
+        <v>122131506</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>78392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572000</v>
+        <v>572090</v>
       </c>
       <c r="R2" t="n">
-        <v>7108033</v>
+        <v>7108068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131560</v>
+        <v>122131620</v>
       </c>
       <c r="B3" t="n">
-        <v>79270</v>
+        <v>79765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,20 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6461</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572083</v>
+        <v>572081</v>
       </c>
       <c r="R3" t="n">
-        <v>7108040</v>
+        <v>7108048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Alvtegen, Johanna Kühne</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131620</v>
+        <v>122131560</v>
       </c>
       <c r="B4" t="n">
-        <v>79761</v>
+        <v>79274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,20 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572081</v>
+        <v>572083</v>
       </c>
       <c r="R4" t="n">
-        <v>7108048</v>
+        <v>7108040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Johanna Kühne, August Alvtegen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131581</v>
+        <v>122131533</v>
       </c>
       <c r="B5" t="n">
-        <v>78389</v>
+        <v>92100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -978,20 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572092</v>
+        <v>572000</v>
       </c>
       <c r="R5" t="n">
-        <v>7108069</v>
+        <v>7108033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131506</v>
+        <v>122131581</v>
       </c>
       <c r="B6" t="n">
-        <v>78388</v>
+        <v>78393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1079,16 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572090</v>
+        <v>572092</v>
       </c>
       <c r="R6" t="n">
-        <v>7108068</v>
+        <v>7108069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 55559-2023 artfynd.xlsx
+++ b/artfynd/A 55559-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131506</v>
+        <v>122131620</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>79765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572090</v>
+        <v>572081</v>
       </c>
       <c r="R2" t="n">
-        <v>7108068</v>
+        <v>7108048</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131620</v>
+        <v>122131506</v>
       </c>
       <c r="B3" t="n">
-        <v>79765</v>
+        <v>78392</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572081</v>
+        <v>572090</v>
       </c>
       <c r="R3" t="n">
-        <v>7108048</v>
+        <v>7108068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131560</v>
+        <v>122131533</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>92113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572083</v>
+        <v>572000</v>
       </c>
       <c r="R4" t="n">
-        <v>7108040</v>
+        <v>7108033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Kühne, August Alvtegen</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131533</v>
+        <v>122131560</v>
       </c>
       <c r="B5" t="n">
-        <v>92100</v>
+        <v>79274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572000</v>
+        <v>572083</v>
       </c>
       <c r="R5" t="n">
-        <v>7108033</v>
+        <v>7108040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Johanna Kühne, August Alvtegen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
